--- a/branches/docs/open-tasks-refresh/StructureDefinition-preview-model.xlsx
+++ b/branches/docs/open-tasks-refresh/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T13:32:01+00:00</t>
+    <t>2026-08-16T13:36:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
